--- a/PinStatus.xlsx
+++ b/PinStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\K\Documents\stu\EC\CAR\TEST\TIcar\TICAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698A9665-8F83-47AA-A970-58EAA1E5F15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9709D4D5-9A0C-4516-A82E-DE86DD545578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t>A</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -95,6 +95,42 @@
   </si>
   <si>
     <t>OLED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HFXIN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HFXOUT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PWMA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AIN1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AIN2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BIN1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BIN2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STBY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>motor</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -102,7 +138,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,8 +161,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -145,8 +189,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -232,11 +282,97 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border diagonalDown="1">
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="medium">
+        <color auto="1"/>
+      </diagonal>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -260,11 +396,48 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -546,109 +719,61 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF7"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="35" width="2.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3"/>
-      <c r="B1" s="6">
+    <row r="1" spans="1:17" s="14" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="11"/>
+      <c r="B1" s="12">
         <v>0</v>
       </c>
-      <c r="C1" s="6">
+      <c r="C1" s="12">
         <v>1</v>
       </c>
-      <c r="D1" s="6">
+      <c r="D1" s="12">
         <v>2</v>
       </c>
-      <c r="E1" s="6">
+      <c r="E1" s="12">
         <v>3</v>
       </c>
-      <c r="F1" s="6">
+      <c r="F1" s="12">
         <v>4</v>
       </c>
-      <c r="G1" s="6">
+      <c r="G1" s="13">
         <v>5</v>
       </c>
-      <c r="H1" s="6">
+      <c r="H1" s="13">
         <v>6</v>
       </c>
-      <c r="I1" s="6">
+      <c r="I1" s="12">
         <v>7</v>
       </c>
-      <c r="J1" s="6">
+      <c r="J1" s="12">
         <v>8</v>
       </c>
-      <c r="K1" s="6">
+      <c r="K1" s="12">
         <v>9</v>
       </c>
-      <c r="L1" s="6">
+      <c r="L1" s="12">
         <v>10</v>
       </c>
-      <c r="M1" s="6">
+      <c r="M1" s="12">
         <v>11</v>
       </c>
-      <c r="N1" s="6">
+      <c r="N1" s="12">
         <v>12</v>
       </c>
-      <c r="O1" s="6">
+      <c r="O1" s="12">
         <v>13</v>
       </c>
-      <c r="P1" s="6">
+      <c r="P1" s="12">
         <v>14</v>
       </c>
-      <c r="Q1" s="6">
-        <v>15</v>
-      </c>
-      <c r="R1" s="6">
-        <v>16</v>
-      </c>
-      <c r="S1" s="6">
-        <v>17</v>
-      </c>
-      <c r="T1" s="6">
-        <v>18</v>
-      </c>
-      <c r="U1" s="6">
-        <v>19</v>
-      </c>
-      <c r="V1" s="6">
-        <v>20</v>
-      </c>
-      <c r="W1" s="6">
-        <v>21</v>
-      </c>
-      <c r="X1" s="6">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="6">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="6">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="6">
-        <v>25</v>
-      </c>
-      <c r="AB1" s="6">
-        <v>26</v>
-      </c>
-      <c r="AC1" s="6">
-        <v>27</v>
-      </c>
-      <c r="AD1" s="6">
-        <v>28</v>
-      </c>
-      <c r="AE1" s="6">
-        <v>29</v>
-      </c>
-      <c r="AF1" s="6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:17" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -656,39 +781,27 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="10"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
-      <c r="Q2" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6"/>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="6"/>
-      <c r="AF2" s="6"/>
-    </row>
-    <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:17" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -707,10 +820,10 @@
       <c r="F3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="21" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="7" t="s">
@@ -718,51 +831,147 @@
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
+      <c r="L3" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="17" t="s">
+        <v>26</v>
+      </c>
       <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="6"/>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="6"/>
-      <c r="AD3" s="6"/>
-      <c r="AE3" s="6"/>
-      <c r="AF3" s="6"/>
-    </row>
-    <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="10" t="s">
+      <c r="P3" s="10"/>
+    </row>
+    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="Q4" s="9" t="s">
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="L4" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+    </row>
+    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12">
+        <v>15</v>
+      </c>
+      <c r="C7" s="12">
+        <v>16</v>
+      </c>
+      <c r="D7" s="12">
+        <v>17</v>
+      </c>
+      <c r="E7" s="12">
         <v>18</v>
       </c>
-      <c r="R4" s="9"/>
-    </row>
-    <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="F7" s="12">
+        <v>19</v>
+      </c>
+      <c r="G7" s="12">
+        <v>20</v>
+      </c>
+      <c r="H7" s="12">
+        <v>21</v>
+      </c>
+      <c r="I7" s="12">
+        <v>22</v>
+      </c>
+      <c r="J7" s="12">
+        <v>23</v>
+      </c>
+      <c r="K7" s="12">
+        <v>24</v>
+      </c>
+      <c r="L7" s="12">
+        <v>25</v>
+      </c>
+      <c r="M7" s="12">
+        <v>26</v>
+      </c>
+      <c r="N7" s="12">
+        <v>27</v>
+      </c>
+      <c r="O7" s="12">
+        <v>28</v>
+      </c>
+      <c r="P7" s="13">
+        <v>29</v>
+      </c>
+      <c r="Q7" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="9"/>
+    </row>
+    <row r="9" spans="1:17" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B10" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="16"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B4:I4"/>
-    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="L4:N4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PinStatus.xlsx
+++ b/PinStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\K\Documents\stu\EC\CAR\TEST\TIcar\TICAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9709D4D5-9A0C-4516-A82E-DE86DD545578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE70637A-F757-484D-95B0-6C483B8A2BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>A</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -131,6 +131,22 @@
   </si>
   <si>
     <t>motor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E1A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E1B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E2B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E2A</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -170,7 +186,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -195,6 +211,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="13">
     <border>
@@ -372,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -412,31 +434,37 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -719,13 +747,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="35" width="2.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="14" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" s="14" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11"/>
       <c r="B1" s="12">
         <v>0</v>
@@ -773,7 +801,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -781,27 +809,29 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="22" t="s">
+      <c r="F2" s="16"/>
+      <c r="G2" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="15" t="s">
         <v>21</v>
       </c>
       <c r="K2" s="10"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
+      <c r="N2" s="24" t="s">
+        <v>28</v>
+      </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
     </row>
-    <row r="3" spans="1:17" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -820,10 +850,10 @@
       <c r="F3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="18" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="7" t="s">
@@ -831,38 +861,40 @@
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
-      <c r="L3" s="17" t="s">
+      <c r="L3" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="M3" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="17" t="s">
+      <c r="N3" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="6"/>
+      <c r="O3" s="24" t="s">
+        <v>31</v>
+      </c>
       <c r="P3" s="10"/>
     </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="15" t="s">
+    <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="L4" s="18" t="s">
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="L4" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-    </row>
-    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+    </row>
+    <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11"/>
       <c r="B7" s="12">
         <v>15</v>
@@ -912,8 +944,11 @@
       <c r="Q7" s="12">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R7" s="12">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -937,8 +972,11 @@
       <c r="O8" s="10"/>
       <c r="P8" s="10"/>
       <c r="Q8" s="9"/>
-    </row>
-    <row r="9" spans="1:17" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R8" s="25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
@@ -948,10 +986,12 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="6"/>
+      <c r="I9" s="24" t="s">
+        <v>29</v>
+      </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
@@ -961,11 +1001,11 @@
       <c r="P9" s="10"/>
       <c r="Q9" s="10"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="16" t="s">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B10" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="16"/>
+      <c r="C10" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="3">
